--- a/Excel/stocks-to-input.xlsx
+++ b/Excel/stocks-to-input.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B92"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +443,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AMATA</t>
+          <t>BAM</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ANAN</t>
+          <t>BANPU</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -463,7 +463,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>BEM</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -473,7 +473,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASP</t>
+          <t>BKIH</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -483,7 +483,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>BPP</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -493,7 +493,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BAM</t>
+          <t>CRC</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -503,7 +503,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BANPU</t>
+          <t>DCON</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -513,7 +513,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>GUNKUL</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -523,7 +523,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BDMS</t>
+          <t>HFT</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -533,7 +533,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BEAUTY</t>
+          <t>HTC</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -543,7 +543,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BEC</t>
+          <t>III</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -553,7 +553,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BEM</t>
+          <t>IMH</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -563,7 +563,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BGRIM</t>
+          <t>IP</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -573,7 +573,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BH</t>
+          <t>KBANK</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -583,7 +583,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BJC</t>
+          <t>KGI</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BKIH</t>
+          <t>LALIN</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -603,7 +603,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BPP</t>
+          <t>ONEE</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -613,7 +613,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>RBF</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -623,7 +623,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHG</t>
+          <t>SAWAD</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -633,7 +633,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CK</t>
+          <t>SIRI</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -643,7 +643,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CPALL</t>
+          <t>SPRC</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -653,7 +653,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CPF</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -663,7 +663,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CPNCG</t>
+          <t>SUPER</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -673,7 +673,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CPNREIT</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -683,7 +683,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CRC</t>
+          <t>TYCN</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -693,7 +693,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DCON</t>
+          <t>UTP</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -703,7 +703,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DIF</t>
+          <t>VIBHA</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -713,640 +713,10 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>WICE</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>EGCO</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>FSMART</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>GFPT</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>GUNKUL</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>HANA</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>HFT</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>HTC</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ICHI</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>IMH</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>KBANK</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>KGI</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>LALIN</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>LPN</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MAJOR</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MBAX</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MEGA</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>NOBLE</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>ONEE</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>ORI</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>OSP</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>PLANB</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>POPF</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>PREB</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>PRM</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>PSH</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>PTG</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>PTT</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>RATCH</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>RBF</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>RJH</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>ROJNA</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>SAWAD</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>SENA</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>SIRI</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>SJWD</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>SPCG</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>SPRC</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>SSP</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>STA</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>STGT</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>SUPER</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>SUPEREIF</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>TIDLOR</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>TIPH</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>TKN</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>TMT</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>TOA</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>TOP</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>TPIPL</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>TQM</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>TSE</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>TTW</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TVO</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>TYCN</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>UTP</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>VIBHA</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>WHAIR</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>WICE</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
         <v>3</v>
       </c>
     </row>
